--- a/SGC-CKN/Excel/126d2cda-554b-4aa1-b6d1-2c2bf6ce8e87_Lô_CT-02_P14-5_D800_31-03-2026.xlsx
+++ b/SGC-CKN/Excel/126d2cda-554b-4aa1-b6d1-2c2bf6ce8e87_Lô_CT-02_P14-5_D800_31-03-2026.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="62">
   <si>
     <t>Dự án</t>
   </si>
@@ -92,31 +92,24 @@
     <t>Ghi chú</t>
   </si>
   <si>
-    <t>Đất lấp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20:35
-30/03/2026</t>
+    <t>1</t>
+  </si>
+  <si>
+    <t>Sét pha, xám nâu, TT dẻo mềm</t>
   </si>
   <si>
     <t xml:space="preserve">20:40
 30/03/2026</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>Sét pha, xám nâu, TT dẻo mềm</t>
-  </si>
-  <si>
     <t xml:space="preserve">21:20
 30/03/2026</t>
   </si>
   <si>
-    <t>3</t>
+    <t/>
+  </si>
+  <si>
+    <t>2</t>
   </si>
   <si>
     <t>Sét lẫn hữu cơ, xám nâu, xám đen TT dẻo chảy</t>
@@ -126,64 +119,64 @@
 30/03/2026</t>
   </si>
   <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>Sét- đôi chỗ kẹp cát pha, lẫn dăm sạn TT dẻo mềm</t>
+  </si>
+  <si>
     <t xml:space="preserve">00:00
-30/03/2026</t>
+31/03/2026</t>
   </si>
   <si>
     <t>4</t>
   </si>
   <si>
-    <t>Sét- đôi chỗ kẹp cát pha, lẫn dăm sạn TT dẻo mềm</t>
+    <t>Sét xám vàng, nâu vàng xám xanh TT nửa cứng</t>
   </si>
   <si>
     <t xml:space="preserve">01:00
-30/03/2026</t>
+31/03/2026</t>
   </si>
   <si>
     <t>5</t>
   </si>
   <si>
-    <t>Sét xám vàng, nâu vàng xám xanh TT nửa cứng</t>
+    <t>Sét pha, xám xanh, xám ghi, TT dẻo mềm lẫn hữu cơ, kẹp cát</t>
   </si>
   <si>
     <t xml:space="preserve">01:40
-30/03/2026</t>
+31/03/2026</t>
   </si>
   <si>
     <t>6</t>
   </si>
   <si>
-    <t>Sét pha, xám xanh, xám ghi, TT dẻo mềm lẫn hữu cơ, kẹp cát</t>
+    <t>Cát pha, xám vàng, xám ghi TT dẻo</t>
   </si>
   <si>
     <t xml:space="preserve">02:20
-30/03/2026</t>
+31/03/2026</t>
   </si>
   <si>
     <t>7</t>
   </si>
   <si>
-    <t>Cát pha, xám vàng, xám ghi TT dẻo</t>
+    <t>Cát thô vừa, KC chặt vừa lẫn sỏi sạn, có chỗ là hạt cát nhỏ bụi</t>
   </si>
   <si>
     <t xml:space="preserve">05:10
-30/03/2026</t>
+31/03/2026</t>
   </si>
   <si>
     <t>8</t>
   </si>
   <si>
-    <t>Cát thô vừa, KC chặt vừa lẫn sỏi sạn, có chỗ là hạt cát nhỏ bụi</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
     <t>Sỏi xám vàng, xám xanh TT rất chặt</t>
   </si>
   <si>
     <t xml:space="preserve">07:46
-30/03/2026</t>
+31/03/2026</t>
   </si>
   <si>
     <t>ẢNH BIÊN BẢN GỐC</t>
@@ -220,7 +213,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="17" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -266,12 +259,6 @@
       <name val="Arial"/>
     </font>
     <font>
-      <b/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
       <color rgb="FF7F1D1D"/>
       <sz val="10"/>
       <name val="Arial"/>
@@ -297,11 +284,6 @@
       <name val="Arial"/>
     </font>
     <font>
-      <color rgb="FF831843"/>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
       <b/>
       <color rgb="FFFFFFFF"/>
       <sz val="12"/>
@@ -314,7 +296,7 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="18">
+  <fills count="16">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -343,7 +325,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD1FAE5"/>
+        <fgColor rgb="FFFFF7ED"/>
       </patternFill>
     </fill>
     <fill>
@@ -353,17 +335,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFF7ED"/>
+        <fgColor rgb="FFD1FAE5"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFA7F3D0"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC2626"/>
       </patternFill>
     </fill>
     <fill>
@@ -389,11 +366,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFA5F3FC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBCFE8"/>
       </patternFill>
     </fill>
     <fill>
@@ -489,7 +461,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -539,6 +511,12 @@
     <xf numFmtId="0" fontId="8" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -575,31 +553,13 @@
     <xf numFmtId="0" fontId="12" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="17" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="17" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -625,7 +585,7 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>22</xdr:row>
+      <xdr:row>21</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="8096250" cy="10477500"/>
@@ -985,7 +945,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K82"/>
+  <dimension ref="A1:K81"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -1176,328 +1136,294 @@
         <v>11</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F11" s="5">
         <v>0</v>
       </c>
       <c r="G11" s="5">
-        <v>-10.72</v>
+        <v>-2.32</v>
       </c>
       <c r="H11" s="5">
-        <v>0.08</v>
+        <v>0.67</v>
       </c>
       <c r="I11" s="5">
-        <v>10.72</v>
+        <v>2.32</v>
       </c>
       <c r="J11" s="8">
-        <v>128.64</v>
+        <v>3.48</v>
       </c>
       <c r="K11" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="12" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B12" s="9" t="s">
         <v>11</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F12" s="9">
-        <v>-10.72</v>
+        <v>-2.32</v>
       </c>
       <c r="G12" s="9">
-        <v>-12.32</v>
+        <v>-12.52</v>
       </c>
       <c r="H12" s="9">
-        <v>0.67</v>
+        <v>1.67</v>
       </c>
       <c r="I12" s="9">
-        <v>1.6</v>
+        <v>10.2</v>
       </c>
       <c r="J12" s="12">
-        <v>2.4</v>
+        <v>6.12</v>
       </c>
       <c r="K12" s="10" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B13" s="13" t="s">
         <v>11</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D13" s="15" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E13" s="15" t="s">
         <v>36</v>
       </c>
       <c r="F13" s="13">
-        <v>-12.32</v>
+        <v>-12.52</v>
       </c>
       <c r="G13" s="13">
-        <v>-12.52</v>
+        <v>-17.72</v>
       </c>
       <c r="H13" s="13">
         <v>1</v>
       </c>
       <c r="I13" s="13">
-        <v>0.2</v>
-      </c>
-      <c r="J13" s="16">
-        <v>0.2</v>
+        <v>5.2</v>
+      </c>
+      <c r="J13" s="12">
+        <v>5.2</v>
       </c>
       <c r="K13" s="14" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A14" s="17" t="s">
+      <c r="A14" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="B14" s="17" t="s">
+      <c r="B14" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="C14" s="18" t="s">
+      <c r="C14" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="D14" s="19" t="s">
+      <c r="D14" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="E14" s="19" t="s">
+      <c r="E14" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="F14" s="17">
-        <v>-12.52</v>
-      </c>
-      <c r="G14" s="17">
+      <c r="F14" s="16">
         <v>-17.72</v>
       </c>
-      <c r="H14" s="17">
+      <c r="G14" s="16">
+        <v>-28.42</v>
+      </c>
+      <c r="H14" s="16">
         <v>1</v>
       </c>
-      <c r="I14" s="17">
-        <v>5.2</v>
-      </c>
-      <c r="J14" s="8">
-        <v>5.2</v>
-      </c>
-      <c r="K14" s="18" t="s">
-        <v>29</v>
+      <c r="I14" s="16">
+        <v>10.7</v>
+      </c>
+      <c r="J14" s="12">
+        <v>10.7</v>
+      </c>
+      <c r="K14" s="17" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="15" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A15" s="20" t="s">
+      <c r="A15" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="B15" s="20" t="s">
+      <c r="B15" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="C15" s="21" t="s">
+      <c r="C15" s="20" t="s">
         <v>41</v>
       </c>
-      <c r="D15" s="22" t="s">
+      <c r="D15" s="21" t="s">
         <v>39</v>
       </c>
-      <c r="E15" s="22" t="s">
+      <c r="E15" s="21" t="s">
         <v>42</v>
       </c>
-      <c r="F15" s="20">
-        <v>-17.72</v>
-      </c>
-      <c r="G15" s="20">
+      <c r="F15" s="19">
         <v>-28.42</v>
       </c>
-      <c r="H15" s="20">
+      <c r="G15" s="19">
+        <v>-35.22</v>
+      </c>
+      <c r="H15" s="19">
         <v>0.67</v>
       </c>
-      <c r="I15" s="20">
-        <v>10.7</v>
-      </c>
-      <c r="J15" s="8">
-        <v>16.05</v>
-      </c>
-      <c r="K15" s="21" t="s">
-        <v>29</v>
+      <c r="I15" s="19">
+        <v>6.8</v>
+      </c>
+      <c r="J15" s="12">
+        <v>10.2</v>
+      </c>
+      <c r="K15" s="20" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="16" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A16" s="23" t="s">
+      <c r="A16" s="22" t="s">
         <v>43</v>
       </c>
-      <c r="B16" s="23" t="s">
+      <c r="B16" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="C16" s="24" t="s">
+      <c r="C16" s="23" t="s">
         <v>44</v>
       </c>
-      <c r="D16" s="25" t="s">
+      <c r="D16" s="24" t="s">
         <v>42</v>
       </c>
-      <c r="E16" s="25" t="s">
+      <c r="E16" s="24" t="s">
         <v>45</v>
       </c>
-      <c r="F16" s="23">
-        <v>-28.42</v>
-      </c>
-      <c r="G16" s="23">
+      <c r="F16" s="22">
         <v>-35.22</v>
       </c>
-      <c r="H16" s="23">
+      <c r="G16" s="22">
+        <v>-37.72</v>
+      </c>
+      <c r="H16" s="22">
         <v>0.67</v>
       </c>
-      <c r="I16" s="23">
-        <v>6.8</v>
+      <c r="I16" s="22">
+        <v>2.5</v>
       </c>
       <c r="J16" s="8">
-        <v>10.2</v>
-      </c>
-      <c r="K16" s="24" t="s">
-        <v>29</v>
+        <v>3.75</v>
+      </c>
+      <c r="K16" s="23" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="17" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A17" s="26" t="s">
+      <c r="A17" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="B17" s="26" t="s">
+      <c r="B17" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="C17" s="27" t="s">
+      <c r="C17" s="26" t="s">
         <v>47</v>
       </c>
-      <c r="D17" s="28" t="s">
+      <c r="D17" s="27" t="s">
         <v>45</v>
       </c>
-      <c r="E17" s="28" t="s">
+      <c r="E17" s="27" t="s">
         <v>48</v>
       </c>
-      <c r="F17" s="26">
-        <v>-35.22</v>
-      </c>
-      <c r="G17" s="26">
+      <c r="F17" s="25">
         <v>-37.72</v>
       </c>
-      <c r="H17" s="26">
+      <c r="G17" s="25">
+        <v>-44.1</v>
+      </c>
+      <c r="H17" s="25">
         <v>2.83</v>
       </c>
-      <c r="I17" s="26">
-        <v>2.5</v>
-      </c>
-      <c r="J17" s="16">
-        <v>0.88</v>
-      </c>
-      <c r="K17" s="27" t="s">
-        <v>29</v>
+      <c r="I17" s="25">
+        <v>6.38</v>
+      </c>
+      <c r="J17" s="8">
+        <v>2.25</v>
+      </c>
+      <c r="K17" s="26" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="18" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A18" s="29" t="s">
+      <c r="A18" s="28" t="s">
         <v>49</v>
       </c>
-      <c r="B18" s="29" t="s">
+      <c r="B18" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="C18" s="30" t="s">
+      <c r="C18" s="29" t="s">
         <v>50</v>
       </c>
-      <c r="D18" s="31" t="s">
-        <v>45</v>
-      </c>
-      <c r="E18" s="31" t="s">
+      <c r="D18" s="30" t="s">
         <v>48</v>
       </c>
-      <c r="F18" s="29">
-        <v>-37.72</v>
-      </c>
-      <c r="G18" s="29">
+      <c r="E18" s="30" t="s">
+        <v>51</v>
+      </c>
+      <c r="F18" s="28">
         <v>-44.1</v>
       </c>
-      <c r="H18" s="29">
-        <v>2.83</v>
-      </c>
-      <c r="I18" s="29">
-        <v>6.38</v>
-      </c>
-      <c r="J18" s="12">
-        <v>2.25</v>
-      </c>
-      <c r="K18" s="30" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="19" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A19" s="32" t="s">
-        <v>51</v>
-      </c>
-      <c r="B19" s="32" t="s">
-        <v>11</v>
-      </c>
-      <c r="C19" s="33" t="s">
+      <c r="G18" s="28">
+        <v>-49.74</v>
+      </c>
+      <c r="H18" s="28">
+        <v>2.6</v>
+      </c>
+      <c r="I18" s="28">
+        <v>5.64</v>
+      </c>
+      <c r="J18" s="8">
+        <v>2.17</v>
+      </c>
+      <c r="K18" s="29" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="21" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A21" s="31" t="s">
         <v>52</v>
       </c>
-      <c r="D19" s="34" t="s">
-        <v>48</v>
-      </c>
-      <c r="E19" s="34" t="s">
-        <v>53</v>
-      </c>
-      <c r="F19" s="32">
-        <v>-44.1</v>
-      </c>
-      <c r="G19" s="32">
-        <v>-49.74</v>
-      </c>
-      <c r="H19" s="32">
-        <v>2.6</v>
-      </c>
-      <c r="I19" s="32">
-        <v>5.64</v>
-      </c>
-      <c r="J19" s="12">
-        <v>2.17</v>
-      </c>
-      <c r="K19" s="33" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="22" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A22" s="35" t="s">
-        <v>54</v>
-      </c>
-      <c r="B22" s="35"/>
-      <c r="C22" s="35"/>
-      <c r="D22" s="35"/>
-      <c r="E22" s="35"/>
-      <c r="F22" s="35"/>
-      <c r="G22" s="35"/>
-      <c r="H22" s="35"/>
-      <c r="I22" s="35"/>
-      <c r="J22" s="35"/>
-      <c r="K22" s="35"/>
-    </row>
+      <c r="B21" s="31"/>
+      <c r="C21" s="31"/>
+      <c r="D21" s="31"/>
+      <c r="E21" s="31"/>
+      <c r="F21" s="31"/>
+      <c r="G21" s="31"/>
+      <c r="H21" s="31"/>
+      <c r="I21" s="31"/>
+      <c r="J21" s="31"/>
+      <c r="K21" s="31"/>
+    </row>
+    <row r="22" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="23" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="24" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="25" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -1557,7 +1483,6 @@
     <row r="79" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="80" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="81" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="82" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="9">
     <mergeCell ref="B1:K1"/>
@@ -1568,7 +1493,7 @@
     <mergeCell ref="B6:K6"/>
     <mergeCell ref="B7:K7"/>
     <mergeCell ref="B8:K8"/>
-    <mergeCell ref="A22:K22"/>
+    <mergeCell ref="A21:K21"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -1578,7 +1503,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -1591,31 +1516,31 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C1" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>60</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1626,7 +1551,7 @@
         <v>11</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D2" s="5">
         <v>1</v>
@@ -1635,16 +1560,16 @@
         <v>0</v>
       </c>
       <c r="F2" s="5">
-        <v>-10.72</v>
+        <v>-2.32</v>
       </c>
       <c r="G2" s="5">
-        <v>0.08</v>
+        <v>0.67</v>
       </c>
       <c r="H2" s="5">
-        <v>10.72</v>
+        <v>2.32</v>
       </c>
       <c r="I2" s="8">
-        <v>128.64</v>
+        <v>3.48</v>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1655,25 +1580,25 @@
         <v>11</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D3" s="9">
         <v>1</v>
       </c>
       <c r="E3" s="9">
-        <v>-10.72</v>
+        <v>-2.32</v>
       </c>
       <c r="F3" s="9">
-        <v>-12.32</v>
+        <v>-12.52</v>
       </c>
       <c r="G3" s="9">
-        <v>0.67</v>
+        <v>1.67</v>
       </c>
       <c r="H3" s="9">
-        <v>1.6</v>
+        <v>10.2</v>
       </c>
       <c r="I3" s="12">
-        <v>2.4</v>
+        <v>6.12</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1684,228 +1609,199 @@
         <v>11</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D4" s="13">
         <v>1</v>
       </c>
       <c r="E4" s="13">
-        <v>-12.32</v>
+        <v>-12.52</v>
       </c>
       <c r="F4" s="13">
-        <v>-12.52</v>
+        <v>-17.72</v>
       </c>
       <c r="G4" s="13">
         <v>1</v>
       </c>
       <c r="H4" s="13">
-        <v>0.2</v>
-      </c>
-      <c r="I4" s="16">
-        <v>0.2</v>
+        <v>5.2</v>
+      </c>
+      <c r="I4" s="12">
+        <v>5.2</v>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="17">
+      <c r="A5" s="16">
         <v>4</v>
       </c>
-      <c r="B5" s="17" t="s">
+      <c r="B5" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="18" t="s">
+      <c r="C5" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="D5" s="17">
+      <c r="D5" s="16">
         <v>1</v>
       </c>
-      <c r="E5" s="17">
-        <v>-12.52</v>
-      </c>
-      <c r="F5" s="17">
+      <c r="E5" s="16">
         <v>-17.72</v>
       </c>
-      <c r="G5" s="17">
+      <c r="F5" s="16">
+        <v>-28.42</v>
+      </c>
+      <c r="G5" s="16">
         <v>1</v>
       </c>
-      <c r="H5" s="17">
-        <v>5.2</v>
-      </c>
-      <c r="I5" s="8">
-        <v>5.2</v>
+      <c r="H5" s="16">
+        <v>10.7</v>
+      </c>
+      <c r="I5" s="12">
+        <v>10.7</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="20">
+      <c r="A6" s="19">
         <v>5</v>
       </c>
-      <c r="B6" s="20" t="s">
+      <c r="B6" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="21" t="s">
+      <c r="C6" s="20" t="s">
         <v>41</v>
       </c>
-      <c r="D6" s="20">
+      <c r="D6" s="19">
         <v>1</v>
       </c>
-      <c r="E6" s="20">
-        <v>-17.72</v>
-      </c>
-      <c r="F6" s="20">
+      <c r="E6" s="19">
         <v>-28.42</v>
       </c>
-      <c r="G6" s="20">
+      <c r="F6" s="19">
+        <v>-35.22</v>
+      </c>
+      <c r="G6" s="19">
         <v>0.67</v>
       </c>
-      <c r="H6" s="20">
-        <v>10.7</v>
-      </c>
-      <c r="I6" s="8">
-        <v>16.05</v>
+      <c r="H6" s="19">
+        <v>6.8</v>
+      </c>
+      <c r="I6" s="12">
+        <v>10.2</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="23">
+      <c r="A7" s="22">
         <v>6</v>
       </c>
-      <c r="B7" s="23" t="s">
+      <c r="B7" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="24" t="s">
+      <c r="C7" s="23" t="s">
         <v>44</v>
       </c>
-      <c r="D7" s="23">
+      <c r="D7" s="22">
         <v>1</v>
       </c>
-      <c r="E7" s="23">
-        <v>-28.42</v>
-      </c>
-      <c r="F7" s="23">
+      <c r="E7" s="22">
         <v>-35.22</v>
       </c>
-      <c r="G7" s="23">
+      <c r="F7" s="22">
+        <v>-37.72</v>
+      </c>
+      <c r="G7" s="22">
         <v>0.67</v>
       </c>
-      <c r="H7" s="23">
-        <v>6.8</v>
+      <c r="H7" s="22">
+        <v>2.5</v>
       </c>
       <c r="I7" s="8">
-        <v>10.2</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="26">
+      <c r="A8" s="25">
         <v>7</v>
       </c>
-      <c r="B8" s="26" t="s">
+      <c r="B8" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="C8" s="27" t="s">
+      <c r="C8" s="26" t="s">
         <v>47</v>
       </c>
-      <c r="D8" s="26">
+      <c r="D8" s="25">
         <v>1</v>
       </c>
-      <c r="E8" s="26">
-        <v>-35.22</v>
-      </c>
-      <c r="F8" s="26">
+      <c r="E8" s="25">
         <v>-37.72</v>
       </c>
-      <c r="G8" s="26">
+      <c r="F8" s="25">
+        <v>-44.1</v>
+      </c>
+      <c r="G8" s="25">
         <v>2.83</v>
       </c>
-      <c r="H8" s="26">
-        <v>2.5</v>
-      </c>
-      <c r="I8" s="16">
-        <v>0.88</v>
+      <c r="H8" s="25">
+        <v>6.38</v>
+      </c>
+      <c r="I8" s="8">
+        <v>2.25</v>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="29">
+      <c r="A9" s="28">
         <v>8</v>
       </c>
-      <c r="B9" s="29" t="s">
+      <c r="B9" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="C9" s="30" t="s">
+      <c r="C9" s="29" t="s">
         <v>50</v>
       </c>
-      <c r="D9" s="29">
+      <c r="D9" s="28">
         <v>1</v>
       </c>
-      <c r="E9" s="29">
-        <v>-37.72</v>
-      </c>
-      <c r="F9" s="29">
+      <c r="E9" s="28">
         <v>-44.1</v>
       </c>
-      <c r="G9" s="29">
-        <v>2.83</v>
-      </c>
-      <c r="H9" s="29">
-        <v>6.38</v>
-      </c>
-      <c r="I9" s="12">
-        <v>2.25</v>
-      </c>
-    </row>
-    <row r="10" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="32">
-        <v>9</v>
-      </c>
-      <c r="B10" s="32" t="s">
-        <v>11</v>
+      <c r="F9" s="28">
+        <v>-49.74</v>
+      </c>
+      <c r="G9" s="28">
+        <v>2.6</v>
+      </c>
+      <c r="H9" s="28">
+        <v>5.64</v>
+      </c>
+      <c r="I9" s="8">
+        <v>2.17</v>
+      </c>
+    </row>
+    <row r="10" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" s="32" t="s">
+        <v>61</v>
+      </c>
+      <c r="B10" s="33" t="s">
+        <v>30</v>
       </c>
       <c r="C10" s="33" t="s">
-        <v>52</v>
-      </c>
-      <c r="D10" s="32">
-        <v>1</v>
-      </c>
-      <c r="E10" s="32">
-        <v>-44.1</v>
-      </c>
-      <c r="F10" s="32">
+        <v>30</v>
+      </c>
+      <c r="D10" s="33">
+        <v>8</v>
+      </c>
+      <c r="E10" s="33">
+        <v>0</v>
+      </c>
+      <c r="F10" s="33">
         <v>-49.74</v>
       </c>
-      <c r="G10" s="32">
-        <v>2.6</v>
-      </c>
-      <c r="H10" s="32">
-        <v>5.64</v>
-      </c>
-      <c r="I10" s="12">
-        <v>2.17</v>
-      </c>
-    </row>
-    <row r="11" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="36" t="s">
-        <v>63</v>
-      </c>
-      <c r="B11" s="37" t="s">
-        <v>29</v>
-      </c>
-      <c r="C11" s="37" t="s">
-        <v>29</v>
-      </c>
-      <c r="D11" s="37">
-        <v>9</v>
-      </c>
-      <c r="E11" s="37">
-        <v>0</v>
-      </c>
-      <c r="F11" s="37">
-        <v>-49.74</v>
-      </c>
-      <c r="G11" s="37">
-        <v>12.35</v>
-      </c>
-      <c r="H11" s="37">
+      <c r="G10" s="33">
+        <v>11.1</v>
+      </c>
+      <c r="H10" s="33">
         <v>49.74</v>
       </c>
-      <c r="I11" s="37">
-        <v>4.03</v>
+      <c r="I10" s="33">
+        <v>4.48</v>
       </c>
     </row>
   </sheetData>
